--- a/static/standards-correlations/Arkansas_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/Arkansas_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$64</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | Arkansas standards effective July 2025</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | Arkansas standards effective July 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -659,7 +660,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Discovery Coding 2 addresses how professional programmers actually spend their time; Ext 5.3H (Find the Community) surfaces real practitioner repositories. Structured career-path research is absent.</t>
+          <t>Introductory Coding 2 addresses how professional programmers actually spend their time; Ext 5.3H (Find the Community) surfaces real practitioner repositories. Structured career-path research is absent.</t>
         </is>
       </c>
     </row>
@@ -745,7 +746,7 @@
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems covers privacy, online conduct, and societal impact at an elementary level. Algorithmic bias is not covered.</t>
+          <t>Introductory Systems covers privacy, online conduct, and societal impact at an elementary level. Algorithmic bias is not covered.</t>
         </is>
       </c>
     </row>
@@ -878,7 +879,7 @@
       </c>
       <c r="I10" s="8" t="inlineStr">
         <is>
-          <t>Automation is the premise of the entire curriculum. Discovery Systems 3 has students decide what should be autonomous versus human-controlled.</t>
+          <t>Automation is the premise of the entire curriculum. Introductory Systems 3 has students decide what should be autonomous versus human-controlled.</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1016,7 @@
       </c>
       <c r="I13" s="8" t="inlineStr">
         <is>
-          <t>Unit 1.4 is built on this. Discovery Coding 9 has students convert hardcoded values into named variables.</t>
+          <t>Unit 1.4 is built on this. Introductory Coding 9 has students convert hardcoded values into named variables.</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1235,7 @@
       </c>
       <c r="I18" s="8" t="inlineStr">
         <is>
-          <t>Unit 1.1 has students trace literal execution against intent. Discovery Systems 4 teaches flowchart symbols and decision points.</t>
+          <t>Unit 1.1 has students trace literal execution against intent. Introductory Systems 4 teaches flowchart symbols and decision points.</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2784,7 @@
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 10 covers phishing and why emotional pressure works. Ext 5.3G (Secret Messages / HTTPS) covers interception of credentials.</t>
+          <t>Introductory Systems 10 covers phishing and why emotional pressure works. Ext 5.3G (Secret Messages / HTTPS) covers interception of credentials.</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2878,7 @@
       </c>
       <c r="I55" s="8" t="inlineStr">
         <is>
-          <t>Ext 1.1F (Why a PIN?) analyses why a longer password is stronger practice, and Discovery Systems 10 covers recognising manipulation.</t>
+          <t>Ext 1.1F (Why a PIN?) analyses why a longer password is stronger practice, and Introductory Systems 10 covers recognising manipulation.</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2972,7 @@
       </c>
       <c r="I57" s="8" t="inlineStr">
         <is>
-          <t>Ext 3.1F (Compiled, Typed, and Running on Something) contrasts compiled and interpreted execution and what runs the compiled result, alongside Discovery Systems 8 on hardware against software.</t>
+          <t>Ext 3.1F (Compiled, Typed, and Running on Something) contrasts compiled and interpreted execution and what runs the compiled result, alongside Introductory Systems 8 on hardware against software.</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3144,7 @@
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Discovery Systems 9 covers senders, receivers, and common protocols at an elementary level. The remaining concepts are not covered.</t>
+          <t>Introductory Systems 9 covers senders, receivers, and common protocols at an elementary level. The remaining concepts are not covered.</t>
         </is>
       </c>
     </row>
@@ -3318,6 +3319,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -3362,7 +3364,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3376,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -3474,6 +3476,8 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
@@ -3491,7 +3495,7 @@
 LABELS: Strand and focus-area titles in columns B and C are DESCRIPTIVE labels assigned for this crosswalk. The source provides numeric identifiers only. Confirm official strand titles against ADE.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+This crosswalk scores against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 An earlier revision of this file scored lab FRONT MATTER ONLY (headings, descriptions, concept tags, objectives) and materially undercounted coverage. Those figures are superseded.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?' in the labs), or where the standard is only partly met. Cells citing 'Ext N.NL' identify the specific extension carrying the evidence, so a reviewer can verify placement and decide whether optional work counts for their purposes.</t>
         </is>
